--- a/daily_matches/job_matches_2026-10-07.xlsx
+++ b/daily_matches/job_matches_2026-10-07.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect-5</t>
+          <t>Senior Machine Learning Engineer, Fraud Risk Modeling</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, ChromaDB</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, scikit-learn, Docker, Kubernetes, Git, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f4e7353d156d21</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1b0bc837735bcf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>AWS DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, S3, EC2, Glue, Redshift, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,102 +519,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6df5544e897e890</t>
+          <t>https://www.indeed.com/viewjob?jk=20ae1a526db03909</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Sr AI Customer Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, Glue, Synapse, Data Lake, MLflow, Docker, Kubernetes, Apache Airflow</t>
+          <t>Generative AI, RAG, Gemini, Copilot, TensorFlow, PyTorch, BigQuery, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8bb3e07175ba5a</t>
+          <t>https://www.indeed.com/viewjob?jk=12d56dd98ccf656b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Forward-Deployed Engineer (FDE/GTM)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, BigQuery, MLflow, Docker, Kubernetes</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, TensorFlow, PyTorch, FastAPI, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5341b3eae13016</t>
+          <t>https://www.indeed.com/viewjob?jk=36155a5c2444770b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Howard Hughes Medical Institute</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>RAG, S3, BigQuery, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bcc3745577f44</t>
+          <t>https://www.indeed.com/viewjob?jk=97c5e1818487b920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NodeJS/AWS Fullstack developer - Software Engineer</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer, Raleigh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9b6e62814d5305</t>
+          <t>https://www.indeed.com/viewjob?jk=ea97b81f8a8fbea5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Node js/AWS fullstack developerSoftware Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262e6fd34c0f8ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850f4c0879ad3a62</t>
+          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac1512204e679c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64452ea9ee84058</t>
+          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Associate</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, EC2, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MongoDB</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,137 +834,137 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a924de370ac9d076</t>
+          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer – Apply For CircleCard</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python</t>
+          <t>BigQuery, Terraform, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ca3963cee3be6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5131e2f85865e971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GenAI Engineer-3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
+          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c030b480e70d90b</t>
+          <t>https://www.indeed.com/viewjob?jk=9398f49551c5bb4d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-3</t>
+          <t>Full Stack Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb0218a1d6be5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - Observability Platform</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>First Tech Federal Credit Union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cf82ccf38514ed</t>
+          <t>https://www.indeed.com/viewjob?jk=13c0db858176cb52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>California Institute of Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>Data Scientist, RAG, Gemini, FastAPI, Docker, Git, PostgreSQL, Matplotlib, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,19 +1009,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6a45e7ed84165b</t>
+          <t>https://www.indeed.com/viewjob?jk=72d562b5facb7466</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Sr. Information Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1030,46 +1030,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Cortex, MLflow, CI/CD, Jenkins, Terraform, Databricks, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a412cb9f758689</t>
+          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Scientist, Pharmaceutical Supply Chain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Innovate Tech IT LLC</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sheridan, WY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, scikit-learn, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b478fd52cc625f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=227bb5d9c4815669</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Data Engineer – Remote</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YT Global Network</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Hadoop, Cassandra, NoSQL, Python</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,67 +1114,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b02a541e66f4c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b61a7405c84dfffc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SDET (Software Development Engineer in Test)-3</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, BigQuery, CI/CD, Jenkins, Git, BigQuery, Python, SQL</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086b42150c1c6423</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d05244362f989</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,32 +1184,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934be651d2822067</t>
+          <t>https://www.indeed.com/viewjob?jk=d904c2b5f58c6606</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL, Python</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2ab2b60d846cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=47264d648682c4f3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Digital Scientist</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, scikit-learn, Data Lake, Git, Tableau, Power BI, Python</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe49970cad773e80</t>
+          <t>https://www.indeed.com/viewjob?jk=96e1162dafc17ae6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Neuehealth</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Azure ML, Kubernetes, AKS, CI/CD, Databricks, Python, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,32 +1289,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed469eeb22f0314c</t>
+          <t>https://www.indeed.com/viewjob?jk=99557b0ef9c92c11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be020efc616ae06a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e43350da6c2235</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Meetic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdac1dc01d8884d</t>
+          <t>https://www.indeed.com/viewjob?jk=7beb6cd74617ff46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GenAI Developer Sr I</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1192ef8099416b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f26a5e0867808b1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Mid Level</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cenergistic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Copilot, S3, Athena, Docker, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,24 +1429,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06fdb5232c62474</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4b9006e5a261a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>React Native Developer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53df3f7066abea20</t>
+          <t>https://www.indeed.com/viewjob?jk=619459096d05a901</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Incentive Offers</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260ab5e6808866c1</t>
+          <t>https://www.indeed.com/viewjob?jk=532a2d4b82e1603b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Engineer - Stores &amp; Supply Chain</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,34 +1524,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f418a3e9ef70735</t>
+          <t>https://www.indeed.com/viewjob?jk=092b28496b3af73f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,42 +1559,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffeeb6da650ee050</t>
+          <t>https://www.indeed.com/viewjob?jk=218407a1387da551</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Elixir Developer - USA</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e1941605485de6</t>
+          <t>https://www.indeed.com/viewjob?jk=674377c599a842fe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Elixir Developer - USA</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34efbf1abc68bf50</t>
+          <t>https://www.indeed.com/viewjob?jk=49c3498a59b5d74b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Elixir Developer - USA</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1f4cce4b2c559d</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb700de7f228650</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Elixir Developer - USA</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,32 +1709,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a31da046b4bf0732</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f3824a28c34365</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Elixir Developer - USA</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>_coderio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5610f305cdb2a0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f142aa24794da177</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2846833bc59c31c2</t>
+          <t>https://www.indeed.com/viewjob?jk=93197d2c979d8326</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8456a013be9abe6d</t>
+          <t>https://www.indeed.com/viewjob?jk=64f3f84b7d6957ef</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b2eaf336ce0560</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ada3d7fa3fe05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,32 +1884,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea92000540cf9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b764944388dfa0e6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Jenkins, GitHub Actions, Git, Python, R, C++, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,32 +1919,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ce19b12a821d45</t>
+          <t>https://www.indeed.com/viewjob?jk=3230ff0da333eb2e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ee66874ea632bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7f89bbe79ffdc7b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Scientist</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>iRhythm Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, scikit-learn, Git, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,102 +1989,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbcaf60daad9eb76</t>
+          <t>https://www.indeed.com/viewjob?jk=cc220fc74e19de7d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bitsight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e5d4c0ba6bf9cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3187fc969380e49b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer - Stores &amp; Supply Chain</t>
+          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0949974561561535</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3cbad22cfacaf4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Software Engineer III - Backend</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,19 +2094,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5378627ae30a4582</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfe9ad476bd328d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Professional Services Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2115,11 +2115,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Dataflow, Docker, Kubernetes, Terraform, R, Scala</t>
+          <t>RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f07433764ff47c</t>
+          <t>https://www.indeed.com/viewjob?jk=65745051474ea39e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Python Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31614612c22a3bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea7b2258ae68843</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Git, MySQL, Python, SQL, R, Java, C++, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff9b34685f56a71</t>
+          <t>https://www.indeed.com/viewjob?jk=48c9906598dd507a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern, BS/MS - Summer 2027</t>
+          <t>Senior Machine Learning Platform Engineer — Model Hosting &amp; MLOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+          <t>RAG, AWS SageMaker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,32 +2234,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ff914b254cc256</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f9b41775fcfd7e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer, Global Quality</t>
+          <t>2027 Consumer &amp; Community Banking - Risk Modeling Associate Program - Summer Internship</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Git, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, PyTorch, XGBoost, PySpark, Hadoop, Python, SQL, R, Java, C++</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89b5969c209beb5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3446438ab9209e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Full Stack - React)</t>
+          <t>Java Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java, Scala</t>
+          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57d070502efa252e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9f34125a0d7797</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Full Stack - React)</t>
+          <t>AI Automation Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Frost</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>S3, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af66fbc265bff345</t>
+          <t>https://www.indeed.com/viewjob?jk=f4cbae61cfc768f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Analytics Engineer II, Marketing Technology - Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, Python, R, Optimization</t>
+          <t>RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b7716243899cf59</t>
+          <t>https://www.indeed.com/viewjob?jk=238a27c5210ae789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Automation Platform Engineer / DevOps Systems Integration Engineer - Hybrid Plano, TX</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,17 +2399,52 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c00cb91ece5cdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac6c69177b62bd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b3c7fbddfbcdc41</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-07.xlsx
+++ b/daily_matches/job_matches_2026-10-07.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,52 +456,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Fraud Risk Modeling</t>
+          <t>GenAI Application Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, scikit-learn, Docker, Kubernetes, Git, Snowflake, Kafka</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1b0bc837735bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=90552286b3b19301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer (Hybrid)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, S3, EC2, Glue, Redshift, MLflow, Docker, CI/CD</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,59 +519,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ae1a526db03909</t>
+          <t>https://www.indeed.com/viewjob?jk=a88c40e681df4e1a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr AI Customer Engineer</t>
+          <t>Summer 2027 IT Graduate Internship</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Florida Blue (Blue Cross and Blue Shield of Florida)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, TensorFlow, PyTorch, BigQuery, FastAPI, Docker, Kubernetes</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d56dd98ccf656b</t>
+          <t>https://www.indeed.com/viewjob?jk=c03187ebf14c245a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Forward-Deployed Engineer (FDE/GTM)</t>
+          <t>IT Summer 2027 Undergraduate Internship</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Florida Blue (Blue Cross and Blue Shield of Florida)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,42 +579,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, TensorFlow, PyTorch, FastAPI, Git</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36155a5c2444770b</t>
+          <t>https://www.indeed.com/viewjob?jk=43059a5e3a7a4c51</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>GenAI Engineer / Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Howard Hughes Medical Institute</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, BigQuery, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery, PySpark</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, S3, FastAPI, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,24 +624,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c5e1818487b920</t>
+          <t>https://www.indeed.com/viewjob?jk=073e98661976c07a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2027 Capital Markets, Quantitative Technology Services Summer, Raleigh</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,42 +649,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea97b81f8a8fbea5</t>
+          <t>https://www.indeed.com/viewjob?jk=f039d10821c47f2a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,94 +694,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac695015f6e52803</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Data Architecture &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>Redshift, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
+          <t>https://www.indeed.com/viewjob?jk=923379e0dc0b8dde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Erlanger, KY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
+          <t>https://www.indeed.com/viewjob?jk=f50c7dd606761e70</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,34 +789,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Synapse, Data Lake, Dataflow, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, AKS, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
+          <t>https://www.indeed.com/viewjob?jk=30b61d3e2a7507ff</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Software Engineer - FDE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,42 +824,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab280d8a3ea7005</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Full-Stack Software Engineer – Azure Practitioner</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>KCI Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BigQuery, Terraform, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, LLaMA, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131e2f85865e971</t>
+          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4 (AWS, Java/ Python, Database, Go)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9398f49551c5bb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=35ba6de05ae13211</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Analyst</t>
+          <t>Full Stack Software Engineer 4 - Go, Python, Java, AWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
+          <t>https://www.indeed.com/viewjob?jk=42b5b5030b63cf61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,54 +974,54 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c0db858176cb52</t>
+          <t>https://www.indeed.com/viewjob?jk=00983a19f7d4e161</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist, NLP &amp; LLM Fine-Tuning</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>California Institute of Technology</t>
+          <t>Xenoss</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, FastAPI, Docker, Git, PostgreSQL, Matplotlib, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Mistral, Hugging Face, BigQuery, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d562b5facb7466</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6db1448b16a37e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Information Security Engineer</t>
+          <t>Clinician-Developer: Cloud &amp; Integrations</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Charleston Children’s Therapy Center</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, MLflow, CI/CD, Jenkins, Terraform, Databricks, Python</t>
+          <t>RAG, S3, EC2, Docker, AKS, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist, Pharmaceutical Supply Chain</t>
+          <t>AI Engineer in the USA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,34 +1069,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, scikit-learn, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227bb5d9c4815669</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd132658793c448</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>California Institute of Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>Data Scientist, RAG, Gemini, FastAPI, Docker, Git, PostgreSQL, Matplotlib, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,102 +1114,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61a7405c84dfffc</t>
+          <t>https://www.indeed.com/viewjob?jk=b3aca286b447de30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rite-Hite</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, Git, BigQuery, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d05244362f989</t>
+          <t>https://www.indeed.com/viewjob?jk=9d80240292205dab</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EZETECH LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Port Saint Lucie, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>RAG, LLaMA, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d904c2b5f58c6606</t>
+          <t>https://www.indeed.com/viewjob?jk=2d647f03a5d54abd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chroma Enterprise Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>S3, CI/CD, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47264d648682c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a1b1b8f8cb6758</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BULLISH GLOBAL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96e1162dafc17ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a080d784d7abbc6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>AI Engineer 4 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluation)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,32 +1289,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99557b0ef9c92c11</t>
+          <t>https://www.indeed.com/viewjob?jk=eb150d981629517b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluation)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e43350da6c2235</t>
+          <t>https://www.indeed.com/viewjob?jk=21738775ce04217e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb6cd74617ff46</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6c8e2666c1679f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f26a5e0867808b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a62e18781a7adc0f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluation)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4b9006e5a261a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b035428da916080</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluations)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619459096d05a901</t>
+          <t>https://www.indeed.com/viewjob?jk=1faebbd3198b19a3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>AI Engineer 5 (Gen AI Platform Services: Agentic Systems)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532a2d4b82e1603b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa9284bd31eac5e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TransUnion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
+          <t>Data Scientist, RAG, Git, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,917 +1534,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092b28496b3af73f</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=218407a1387da551</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Rosslyn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=674377c599a842fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49c3498a59b5d74b</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb700de7f228650</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f3824a28c34365</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f142aa24794da177</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93197d2c979d8326</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64f3f84b7d6957ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ada3d7fa3fe05</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b764944388dfa0e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3230ff0da333eb2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f89bbe79ffdc7b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc220fc74e19de7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3187fc969380e49b</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Banking Product Forward Deployed Engineer - Innovation_Delivery_Transformation</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3cbad22cfacaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Backend</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfe9ad476bd328d</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65745051474ea39e</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Python Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea7b2258ae68843</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Junior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48c9906598dd507a</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Platform Engineer — Model Hosting &amp; MLOps</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f9b41775fcfd7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2027 Consumer &amp; Community Banking - Risk Modeling Associate Program - Summer Internship</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, XGBoost, PySpark, Hadoop, Python, SQL, R, Java, C++</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3446438ab9209e</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Java Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Citi</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9f34125a0d7797</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AI Automation Engineer II</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Frost</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4cbae61cfc768f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Analytics Engineer II, Marketing Technology - Remote</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>OneDigital</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=238a27c5210ae789</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Full Stack</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac6c69177b62bd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Full Stack</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3c7fbddfbcdc41</t>
+          <t>https://www.indeed.com/viewjob?jk=90063f82121075e6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-07.xlsx
+++ b/daily_matches/job_matches_2026-10-07.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GenAI Application Consultant</t>
+          <t>Senior AWS Agentic AI Engineer – Snowflake</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90552286b3b19301</t>
+          <t>https://www.indeed.com/viewjob?jk=c24d04fca23f04a4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Predictive Sales A.I.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>LangChain, RAG, PyTorch, scikit-learn, Azure ML, Synapse, Docker, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88c40e681df4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1a6eaf40c260e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Summer 2027 IT Graduate Internship</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Florida Blue (Blue Cross and Blue Shield of Florida)</t>
+          <t>Predictive Sales A.I.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, Git, PostgreSQL</t>
+          <t>LangChain, RAG, PyTorch, scikit-learn, Azure ML, Synapse, Docker, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03187ebf14c245a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c03750cbc30f39f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT Summer 2027 Undergraduate Internship</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Florida Blue (Blue Cross and Blue Shield of Florida)</t>
+          <t>DFUSE TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Ai, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, Git, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43059a5e3a7a4c51</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3ef12034fb6c8a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GroundWork Renewables, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,42 +614,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, S3, FastAPI, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, FastAPI, Docker, Apache Airflow, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073e98661976c07a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6dd2f1d6844211</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>Machine Learning Modeling Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL, SQL</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, Keras, MLflow, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,417 +659,417 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039d10821c47f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=da86da9b123c5d5a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>SDC WAMT Senior Backend Engineer---Senior-----Dallas, Raleigh, San Antonio</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac695015f6e52803</t>
+          <t>https://www.indeed.com/viewjob?jk=e65c5560ca576a10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Architecture &amp; Platform Engineering</t>
+          <t>Senior Applied Scientist, Generative AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Redshift, Tableau, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923379e0dc0b8dde</t>
+          <t>https://www.indeed.com/viewjob?jk=75161a481b8f7b2e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Applied Scientist, Generative AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Erlanger, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50c7dd606761e70</t>
+          <t>https://www.indeed.com/viewjob?jk=5735afdb6c2fd681</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Applied Scientist, Generative AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, FastAPI, Docker, AKS, Git, Snowflake, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30b61d3e2a7507ff</t>
+          <t>https://www.indeed.com/viewjob?jk=71a60ccae2e4c127</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Software Engineer - FDE</t>
+          <t>Senior Applied Scientist, Generative AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Terraform, Git, BigQuery, Python, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab280d8a3ea7005</t>
+          <t>https://www.indeed.com/viewjob?jk=01b69f5dba0e374a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Azure Practitioner</t>
+          <t>Senior Applied Scientist, Generative AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KCI Technologies</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
+          <t>https://www.indeed.com/viewjob?jk=a77f4b5cde2c0547</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (AWS, Java/ Python, Database, Go)</t>
+          <t>Senior Applied Scientist, Generative AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ba6de05ae13211</t>
+          <t>https://www.indeed.com/viewjob?jk=20a1383a7d7e57fe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer 4 - Go, Python, Java, AWS</t>
+          <t>AI Forward Deployed Engineer - CRM &amp; Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, FastAPI, Kubernetes, Git, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b5b5030b63cf61</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3479e0a4d7e703</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Thoughtworks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Redshift, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00983a19f7d4e161</t>
+          <t>https://www.indeed.com/viewjob?jk=000d8980128e623a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, NLP &amp; LLM Fine-Tuning</t>
+          <t>SDC WAMT Back End Engineer---Analyst---Dallas, Raleigh, San Antonio</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xenoss</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, Mistral, Hugging Face, BigQuery, BigQuery, Python, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, Kafka, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6db1448b16a37e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c11d949a142a620</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Clinician-Developer: Cloud &amp; Integrations</t>
+          <t>Site Reliability Engineer III – AI-Centric Application Performance &amp; FinOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charleston Children’s Therapy Center</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, AKS, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, BigQuery, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
+          <t>https://www.indeed.com/viewjob?jk=acc60f244ee03aef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer in the USA</t>
+          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,67 +1079,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd132658793c448</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab03e483c84aee8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>California Institute of Technology</t>
+          <t>Augusta University</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, FastAPI, Docker, Git, PostgreSQL, Matplotlib, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3aca286b447de30</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1e877762e988b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AI Data Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rite-Hite</t>
+          <t>Turner &amp; Townsend Pty Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, Git, BigQuery, Kafka, R, Scala</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,229 +1149,229 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d80240292205dab</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b8a1b905d638fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Service Delivery Center, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EZETECH LLC</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Port Saint Lucie, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, Snowflake, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d647f03a5d54abd</t>
+          <t>https://www.indeed.com/viewjob?jk=16371cbe9a6f6a94</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Software Engineer III, AI Agent Builder — FinOps &amp; Technology Cost Value Management</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chroma Enterprise Solutions</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, CI/CD, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Copilot, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1b1b8f8cb6758</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3d9450fb4429ed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Infrastructure Engineer</t>
+          <t>AI Solution Architect - Undergraduate Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BULLISH GLOBAL</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, LLaMA, PyTorch, Docker, Git, Python, R, C++, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a080d784d7abbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=f404bbea1e80e278</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer 4 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluation)</t>
+          <t>IT Analyst III - Cloud Automation and Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Taylorsville, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb150d981629517b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9184edf09372f2a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluation)</t>
+          <t>Senior Software Engineer, Interoperability</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Counterpart Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+          <t>Data Scientist, RAG, BigQuery, Snowflake, BigQuery, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21738775ce04217e</t>
+          <t>https://www.indeed.com/viewjob?jk=f685325d98439c8b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Brightspeed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+          <t>BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6c8e2666c1679f</t>
+          <t>https://www.indeed.com/viewjob?jk=26160681717152b3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory)</t>
+          <t>Software Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Flexion Robotics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1384,34 +1384,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+          <t>RAG, Docker, CI/CD, Git, Python, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62e18781a7adc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bed1850ea629129</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluation)</t>
+          <t>Senior Machine Learning Engineer, ML Infrastructure- Online</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,122 +1419,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b035428da916080</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AI Engineer 5 (Gen AI Platform Services: Agentic AI, Guardrails, Evaluations)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1faebbd3198b19a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI Engineer 5 (Gen AI Platform Services: Agentic Systems)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, PyTorch, Python, R, Java, C++, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa9284bd31eac5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>TransUnion</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Python, SQL, R, Java, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90063f82121075e6</t>
+          <t>https://www.indeed.com/viewjob?jk=524aec395443ac4f</t>
         </is>
       </c>
     </row>
